--- a/mock_results/FX611H_PR1_Result_20260410.xlsx
+++ b/mock_results/FX611H_PR1_Result_20260410.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,20 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="007F6000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +97,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -158,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -177,14 +199,26 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -552,13 +586,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E16"/>
+  <dimension ref="B1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
@@ -620,7 +654,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 200H (Arrow Lake-H)</t>
+          <t>Intel Core Ultra 200H (Arrow Lake-H) + NVIDIA GeForce RTX 50 Series</t>
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
@@ -634,7 +668,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Windows 11 24H2</t>
+          <t>Windows 11 24H2 (Build 26100)</t>
         </is>
       </c>
       <c r="D7" s="4" t="n"/>
@@ -692,7 +726,7 @@
     <row r="14">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>BD / SKU</t>
+          <t>BD / 料號</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -707,51 +741,73 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Panel</t>
+          <t>Panel / RAM</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>FX611H-AQ001</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Intel Core Ultra 7 265H</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>RTX 5060 8GB</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>15.6" FHD 144Hz</t>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>15.6" FHD 144Hz / 16GB DDR5-5600</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>FX611H-AQ002</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265H</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>RTX 5070 Ti 12GB</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>15.6" FHD 144Hz / 16GB DDR5-5600</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>FX611H-AQ003</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Intel Core Ultra 5 235H</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>RTX 5060 8GB</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>15.6" FHD 144Hz</t>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>15.6" FHD 144Hz / 16GB DDR5-5600</t>
         </is>
       </c>
     </row>
@@ -779,154 +835,200 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>▶  SKU：FX611H-AQ001   |   FX611H-AQ002</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>▶  SKU：FX611H-AQ001   |   FX611H-AQ002   |   FX611H-AQ003</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Test Item</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>FX611H-AQ001</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>FX611H-AQ002</t>
         </is>
       </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>FX611H-AQ003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Cinebench R23 30-loop Multi Median (pts)</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n">
+          <t>Cinebench R23 30-loop — Multi-Core Median (pts)</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
         <v>28480</v>
       </c>
-      <c r="D3" s="8" t="n">
-        <v>25310</v>
+      <c r="D3" s="10" t="n">
+        <v>28350</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>22140</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Cinebench R23 30-loop Multi Max (pts)</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="n">
+          <t>Cinebench R23 30-loop — Multi-Core Max (pts)</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
         <v>29120</v>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>25890</v>
+      <c r="D4" s="10" t="n">
+        <v>28990</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>22780</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Cinebench R23 30-loop Multi Min (pts)</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
+          <t>Cinebench R23 30-loop — Multi-Core Min (pts)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
         <v>27940</v>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>24780</v>
+      <c r="D5" s="10" t="n">
+        <v>27810</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>21560</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="10" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cinebench R23 30-loop Single Median (pts)</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
+          <t>Cinebench R23 30-loop — Single-Core Median (pts)</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
         <v>1945</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>1820</v>
+      <c r="D6" s="10" t="n">
+        <v>1941</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1812</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="10" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Cinebench R23 30-loop Single Max (pts)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
+          <t>Cinebench R23 30-loop — Single-Core Max (pts)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
         <v>1978</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>1851</v>
+      <c r="D7" s="10" t="n">
+        <v>1975</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1841</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="10" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cinebench R23 30-loop Single Min (pts)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
+          <t>Cinebench R23 30-loop — Single-Core Min (pts)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
         <v>1912</v>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>1792</v>
+      <c r="D8" s="10" t="n">
+        <v>1908</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>1783</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="10" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Power Limit (W)</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
+          <t>Power Limit — Turbo Mode (W)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>45</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Power Limit — Standard Mode (W)</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -944,154 +1046,244 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>▶  SKU：FX611H-AQ001   |   FX611H-AQ002</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>▶  SKU：FX611H-AQ001   |   FX611H-AQ002   |   FX611H-AQ003</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Test Item</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>FX611H-AQ001</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>FX611H-AQ002</t>
         </is>
       </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>FX611H-AQ003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Fire Strike (score)</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n">
+          <t>Fire Strike — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
         <v>19240</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="10" t="n">
+        <v>31850</v>
+      </c>
+      <c r="E3" s="10" t="n">
         <v>18970</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Fire Strike Extreme (score)</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="n">
+          <t>Fire Strike — Physics Score</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>32580</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>32410</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>22140</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Fire Strike Extreme — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
         <v>9980</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D5" s="10" t="n">
+        <v>16540</v>
+      </c>
+      <c r="E5" s="10" t="n">
         <v>9820</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Fire Strike Ultra (score)</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Fire Strike Ultra — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
         <v>5530</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D6" s="10" t="n">
+        <v>9210</v>
+      </c>
+      <c r="E6" s="10" t="n">
         <v>5430</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Time Spy (score)</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Time Spy — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
         <v>12560</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D7" s="10" t="n">
+        <v>20980</v>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>12340</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Time Spy Extreme (score)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Time Spy — CPU Score</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>14120</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>14050</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>9810</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Time Spy Extreme — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
         <v>6230</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D9" s="10" t="n">
+        <v>10420</v>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>6110</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Port Royal (score)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Port Royal — Score</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
         <v>8120</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D10" s="10" t="n">
+        <v>13480</v>
+      </c>
+      <c r="E10" s="10" t="n">
         <v>7980</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Speed Way (score)</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Speed Way — Score</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
         <v>3350</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D11" s="10" t="n">
+        <v>5580</v>
+      </c>
+      <c r="E11" s="10" t="n">
         <v>3290</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>DLSS Feature Test (DLSS 4 MFG)</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1109,46 +1301,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>▶  SKU：FX611H-AQ001   |   FX611H-AQ002</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>▶  SKU：FX611H-AQ001   |   FX611H-AQ002   |   FX611H-AQ003</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Test Item</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>FX611H-AQ001</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>FX611H-AQ002</t>
         </is>
       </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>FX611H-AQ003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1156,15 +1354,18 @@
           <t>MobileMark 25 — Modern Office (min)</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="10" t="n">
         <v>682</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="10" t="n">
+        <v>658</v>
+      </c>
+      <c r="E3" s="10" t="n">
         <v>715</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1172,43 +1373,128 @@
           <t>MobileMark 25 — Video Playback (min)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="10" t="n">
         <v>824</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="10" t="n">
+        <v>801</v>
+      </c>
+      <c r="E4" s="10" t="n">
         <v>856</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>MobileMark 25 — Content Creation (min)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>598</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>575</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
           <t>PCMark 10 Battery — Modern Office (min)</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
-        <v>598</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="C6" s="10" t="n">
+        <v>610</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>588</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>PCMark 10 Battery — Video Playback (min)</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C7" s="10" t="n">
         <v>910</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D7" s="10" t="n">
+        <v>892</v>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>942</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Web Browsing (Edge / YouTube) (min)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>542</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>521</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Battery Capacity (Wh)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Charging Time: 0→100% (min)</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1226,154 +1512,276 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>▶  SKU：FX611H-AQ001   |   FX611H-AQ002</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>▶  SKU：FX611H-AQ001   |   FX611H-AQ002   |   FX611H-AQ003</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Test Item</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>FX611H-AQ001</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>FX611H-AQ002</t>
         </is>
       </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>FX611H-AQ003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Cinebench R23 Multi (pts)</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n">
+          <t>Cinebench R23 — Multi-Core (pts)</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
         <v>28350</v>
       </c>
-      <c r="D3" s="8" t="n">
-        <v>25120</v>
+      <c r="D3" s="10" t="n">
+        <v>28210</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>22120</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Cinebench R23 Single (pts)</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="n">
+          <t>Cinebench R23 — Single-Core (pts)</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
         <v>1932</v>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>1815</v>
+      <c r="D4" s="10" t="n">
+        <v>1928</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>1810</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Cinebench R24 Multi (pts)</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
+          <t>Cinebench R24 — Multi-Core (pts)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
         <v>18850</v>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>16790</v>
+      <c r="D5" s="10" t="n">
+        <v>18760</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>14890</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="10" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cinebench R24 Single (pts)</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
+          <t>Cinebench R24 — Single-Core (pts)</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
         <v>1278</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>1201</v>
+      <c r="D6" s="10" t="n">
+        <v>1272</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1198</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="10" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>PCMark 10 Overall (score)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
+          <t>Cinebench 2024 — Multi-Core (pts)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>1515</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>PCMark 10 — Overall (score)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
         <v>8124</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>7893</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>PCMark 10 Productivity (score)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
+      <c r="D8" s="10" t="n">
+        <v>8098</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>7650</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>PCMark 10 — Productivity (score)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
         <v>9546</v>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>9210</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>CrossMark Overall (score)</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
+      <c r="D9" s="10" t="n">
+        <v>9512</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>8920</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>PCMark 10 — Digital Content Creation (score)</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>10280</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>10250</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>9640</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>CrossMark — Overall (score)</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
         <v>2042</v>
       </c>
-      <c r="D9" s="8" t="n">
-        <v>1978</v>
+      <c r="D11" s="10" t="n">
+        <v>2035</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>CrossMark — Productivity (score)</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>2156</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>2148</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>3DMark CPU Profile — 1T (pts)</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>1245</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>1241</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>3DMark CPU Profile — Max Threads (pts)</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>28460</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>28380</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>22050</v>
       </c>
     </row>
   </sheetData>
@@ -1391,207 +1799,529 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>▶  SKU：FX611H-AQ001   |   FX611H-AQ002</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>▶  SKU：FX611H-AQ001   |   FX611H-AQ002   |   FX611H-AQ003</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Test Item</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>FX611H-AQ001</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>FX611H-AQ002</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>FX611H-AQ003</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>GPU →</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>RTX 5060 8GB GDDR7</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>RTX 5070 Ti 12GB GDDR7</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>RTX 5060 8GB GDDR7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>▌ 3DMark Benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>3DMark Fire Strike (score)</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>19340</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>18980</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Fire Strike — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>19240</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>31850</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>18970</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>3DMark Fire Strike Extreme (score)</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="n">
-        <v>10020</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>9850</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Fire Strike — Physics Score</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>32580</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>32410</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>22140</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>3DMark Time Spy (score)</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>12650</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>12420</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Fire Strike Extreme — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>9980</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>16540</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>9820</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>3DMark Time Spy Extreme (score)</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>6380</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>6250</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Fire Strike Ultra — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>5530</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>9210</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>5430</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Cyberpunk 2077 1080p Ultra (fps)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Time Spy — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>12560</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>20980</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>12340</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Time Spy — CPU Score</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>14120</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>14050</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>9810</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Time Spy Extreme — Graphics Score</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>6230</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>10420</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>6110</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Port Royal — Score</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>8120</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>13480</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>7980</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>3DMark Speed Way — Score</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>3350</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>5580</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>▌ Gaming FPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Cyberpunk 2077 — 1080p Ultra RT (fps)</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Cyberpunk 2077 — 1080p Ultra RT + DLSS Quality (fps)</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>148</v>
+      </c>
+      <c r="E16" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Cyberpunk 2077 — 1440p Ultra RT (fps)</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Cyberpunk 2077 — 1440p Ultra RT + DLSS Quality (fps)</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>104</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Alan Wake 2 — 1080p Ultra RT (fps)</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Cyberpunk 2077 1440p Ultra (fps)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Alan Wake 2 — 1080p Ultra RT + DLSS Quality (fps)</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>135</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Red Dead Redemption 2 1080p Ultra (fps)</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>F1 2024 — 1080p Ultra (fps)</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>148</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>198</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Red Dead Redemption 2 1440p Ultra (fps)</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>F1 2024 — 1440p Ultra (fps)</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>142</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>F1 2024 1080p Ultra (fps)</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>CS2 — 1080p High (fps)</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>320</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>340</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>DOTA 2 — 1080p Ultra (fps)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>225</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Red Dead Redemption 2 — 1080p Ultra (fps)</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Elden Ring — 1080p Max Settings (fps)</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>112</v>
+      </c>
+      <c r="D26" s="10" t="n">
         <v>148</v>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>F1 2024 1440p Ultra (fps)</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>101</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>98</v>
+      <c r="E26" s="10" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Black Myth: Wukong — 1080p Epic (fps)</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Black Myth: Wukong — 1080p Epic + DLSS Quality (fps)</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
